--- a/data/trans_orig/IP31B_R_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31B_R_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24973</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18341</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>31600</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>49,22%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>36,15%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>62,28%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>24553</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16610</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>34583</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>46,43%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>31,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>65,39%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27725</t>
+          <t>19520</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20887</t>
+          <t>14099</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34589</t>
+          <t>25693</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>52278</t>
+          <t>44493</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42271</t>
+          <t>35829</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64650</t>
+          <t>52591</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>54,81%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28330</t>
+          <t>25767</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18300</t>
+          <t>19140</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36273</t>
+          <t>32399</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27546</t>
+          <t>25695</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20682</t>
+          <t>19522</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34384</t>
+          <t>31116</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>55876</t>
+          <t>51462</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43504</t>
+          <t>43364</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65883</t>
+          <t>60126</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>62,66%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50740</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50740</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50740</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>52883</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>52883</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>52883</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>55271</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55271</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55271</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>108154</t>
+          <t>95955</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>108154</t>
+          <t>95955</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>108154</t>
+          <t>95955</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>152952</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>132817</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>173498</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>32,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>28,53%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>37,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>152790</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>127563</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>214142</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>33,94%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>28,33%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>47,56%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>176738</t>
+          <t>122696</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>154888</t>
+          <t>108770</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>200259</t>
+          <t>139823</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>329528</t>
+          <t>275648</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>299027</t>
+          <t>249065</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>383166</t>
+          <t>302677</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>312611</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>292065</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>332746</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>67,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>62,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>71,47%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>426</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>297424</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>236072</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>322651</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>66,06%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>52,44%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>71,67%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>392</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>326405</t>
+          <t>300576</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>302884</t>
+          <t>283449</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>348255</t>
+          <t>314502</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>623829</t>
+          <t>613186</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>570191</t>
+          <t>586157</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>654330</t>
+          <t>639769</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>71,98%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>465563</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>465563</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>465563</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>621</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>450214</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>450214</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>450214</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>503143</t>
+          <t>423272</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>503143</t>
+          <t>423272</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>503143</t>
+          <t>423272</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>953357</t>
+          <t>888834</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>953357</t>
+          <t>888834</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>953357</t>
+          <t>888834</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>47933</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>39177</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>59474</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>28,76%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,68%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>42384</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>33344</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>50745</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>29,29%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23,05%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35,07%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>54685</t>
+          <t>41587</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43620</t>
+          <t>31839</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65934</t>
+          <t>49886</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>97069</t>
+          <t>89520</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81852</t>
+          <t>76967</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112398</t>
+          <t>103320</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>118753</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>107212</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>127509</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>71,24%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>64,32%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>76,5%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>102301</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>93940</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>111341</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>70,71%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>64,93%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>76,95%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>126454</t>
+          <t>104006</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>115205</t>
+          <t>95707</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>137519</t>
+          <t>113754</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>228755</t>
+          <t>222759</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>213426</t>
+          <t>208959</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>243972</t>
+          <t>235312</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>75,35%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>144685</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>144685</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>144685</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>145593</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>145593</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>145593</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>325824</t>
+          <t>312279</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>325824</t>
+          <t>312279</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>325824</t>
+          <t>312279</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>225858</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>204522</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>250878</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>33,07%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>29,95%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>36,73%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>289</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>219727</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>192980</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>279990</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>33,92%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>29,79%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>43,22%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>259149</t>
+          <t>183803</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>233608</t>
+          <t>162146</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>202880</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>478876</t>
+          <t>409662</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>442440</t>
+          <t>378268</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>538717</t>
+          <t>440054</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>33,93%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>457130</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>432110</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>478466</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>66,93%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>63,27%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>70,05%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>618</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>428055</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>367792</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>454802</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>66,08%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>56,78%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>70,21%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>480404</t>
+          <t>430277</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>451139</t>
+          <t>411200</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>505945</t>
+          <t>451934</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>908459</t>
+          <t>887406</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>848618</t>
+          <t>857014</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>944895</t>
+          <t>918800</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>70,84%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>907</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>647782</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>647782</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>647782</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>935</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614080</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614080</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614080</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1387335</t>
+          <t>1297068</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1387335</t>
+          <t>1297068</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1387335</t>
+          <t>1297068</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
